--- a/examples/PL-template-PL28.xlsx
+++ b/examples/PL-template-PL28.xlsx
@@ -20,14 +20,28 @@
     <author>Author</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Riga con A vuota = nuovo blocco: nome in B, varianti sotto le alzate.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>Riga con A vuota = nuovo blocco (nome in B, varianti a destra). Tipo di settimana: normale (o vuoto), scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara</t>
+          <t>Date della settimana (testo libero, facoltativo).</t>
         </r>
       </text>
     </comment>
     <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>Tipo di settimana: normale (o vuoto), scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <t>Carico dai massimali: ="4x5 "&amp;MROUND(Massimali!$B$3*0.57,2.5)&amp;"kg" (riga 3 = prima alzata, 0.57 = 57%, arrotondato a 2,5), oppure testo con segnaposto: 4x5 {Squat .57}kg</t>
@@ -44,6 +58,13 @@
     <author>Author</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>Rep e Intensità possono contenere carichi. Carico dai massimali: ="4x5 "&amp;MROUND(Massimali!$B$3*0.57,2.5)&amp;"kg" (riga 3 = prima alzata, 0.57 = 57%, arrotondato a 2,5), oppure testo con segnaposto: 4x5 {Squat .57}kg</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G1" authorId="0">
       <text>
         <r>
@@ -56,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Template PL – formato PL28 (accessori uguali per tutto il blocco)</t>
   </si>
@@ -70,10 +91,13 @@
     <t>• Massimali: nome in colonna A, massimale in colonna B, dalla riga 3. Le formule puntano alla riga: Massimali!$B$3 = prima alzata.</t>
   </si>
   <si>
-    <t>• overall, riga 1: week | fase | una colonna per alzata "Nome (giorno)", es. "Squat (A)".</t>
-  </si>
-  <si>
-    <t>• overall, riga di blocco: A vuota, nome del blocco in B, varianti sotto ogni alzata. Righe di settimana: numero in A (1, 2, 3… senza buchi), tipo in B, prescrizioni.</t>
+    <t>• overall, riga 1: week | giorno | tipo | una colonna per alzata "Nome (giorno)", es. "Squat (A)". Le colonne vuote fanno da separatore.</t>
+  </si>
+  <si>
+    <t>• overall, riga di blocco: A vuota, nome del blocco in B, varianti sotto ogni alzata. Righe di settimana: numero in A (1, 2, 3… senza buchi), date in B (facoltative), tipo in C, prescrizioni.</t>
+  </si>
+  <si>
+    <t>• Righe vuote tra i blocchi vanno bene; due righe vuote di fila chiudono il foglio.</t>
   </si>
   <si>
     <t>• Tipo di settimana (menu a tendina): normale (o vuoto), scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara.</t>
@@ -82,7 +106,7 @@
     <t>• Prescrizioni: testo libero; carichi con la formula ="4x5 "&amp;MROUND(Massimali!$B$3*0.75,2.5)&amp;"kg" oppure col segnaposto 4x5 {Squat .75}kg. Cella vuota = alzata non fatta quella settimana.</t>
   </si>
   <si>
-    <t>• accessori: Giorno | Esercizio | Istruzioni | Gruppo | Rep | Intensità, poi una colonna "Serie B…" per blocco (intero, 0 = non fatto).</t>
+    <t>• accessori: Giorno | Esercizio | Istruzioni | Gruppo | Rep | Intensità, poi una colonna "Serie B…" per blocco (intero, 0 = non fatto). Rep e Intensità possono contenere carichi, come le prescrizioni.</t>
   </si>
   <si>
     <t>• Nelle settimane transizione, scarico e test l'app toglie 1 serie agli accessori e aggiunge 1 al RIR.</t>
@@ -109,7 +133,10 @@
     <t>week</t>
   </si>
   <si>
-    <t>fase</t>
+    <t>giorno</t>
+  </si>
+  <si>
+    <t>tipo</t>
   </si>
   <si>
     <t>Squat (A)</t>
@@ -599,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -658,6 +685,11 @@
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -677,12 +709,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>180</v>
@@ -690,7 +722,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
         <v>120</v>
@@ -698,7 +730,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2">
         <v>210</v>
@@ -706,7 +738,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <f>SUM(B3:B5)</f>
@@ -721,76 +753,82 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="6" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="2" t="str">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="str">
         <f>"4x5 "&amp;MROUND(Massimali!$B$3*0.75,2.5)&amp;"kg"</f>
         <v>4x5 135kg</v>
       </c>
-      <c r="D3" s="2" t="str">
+      <c r="E3" s="2" t="str">
         <f>"5x5 "&amp;MROUND(Massimali!$B$4*0.72,2.5)&amp;"kg"</f>
         <v>5x5 87,5kg</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="2" t="str">
+      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="str">
         <f>MROUND(Massimali!$B$4*0.65,2.5)&amp;"kg 30-35RT"</f>
         <v>77,5kg 30-35RT</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: normale, scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara" sqref="B2:B400">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: normale, scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara" sqref="C2:C400">
       <formula1>"normale,scarico,transizione,ramping,intensificazione,picco,taper,entrata,test,gara"</formula1>
     </dataValidation>
   </dataValidations>
@@ -816,45 +854,45 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2">
         <v>3</v>
@@ -862,20 +900,20 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3" s="2">
         <v>3</v>
@@ -883,20 +921,20 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2">
         <v>3</v>
@@ -925,10 +963,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/examples/PL-template-PL28.xlsx
+++ b/examples/PL-template-PL28.xlsx
@@ -48,6 +48,13 @@
         </r>
       </text>
     </comment>
+    <comment ref="A2" authorId="0">
+      <text>
+        <r>
+          <t>Tipo di ogni alzata (facoltativo, testo libero): stressante, rigenerante, tecnica… L'app lo mostra accanto al nome.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -77,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>Template PL – formato PL28 (accessori uguali per tutto il blocco)</t>
   </si>
@@ -91,7 +98,10 @@
     <t>• Massimali: nome in colonna A, massimale in colonna B, dalla riga 3. Le formule puntano alla riga: Massimali!$B$3 = prima alzata.</t>
   </si>
   <si>
-    <t>• overall, riga 1: week | giorno | tipo | una colonna per alzata "Nome (giorno)", es. "Squat (A)". Le colonne vuote fanno da separatore.</t>
+    <t>• overall, riga 1: week | giorno | tipo | una colonna per alzata "Nome (giorno)", es. "Squat (A)", raggruppate per alzata (Squat A, Squat C… poi Panca). Le colonne vuote fanno da separatore.</t>
+  </si>
+  <si>
+    <t>• overall, riga 2 (facoltativa): "tipo alzata" in A e sotto ogni alzata il suo tipo (stressante, rigenerante, tecnica…, testo libero). L'app lo mostra accanto al nome.</t>
   </si>
   <si>
     <t>• overall, riga di blocco: A vuota, nome del blocco in B, varianti sotto ogni alzata. Righe di settimana: numero in A (1, 2, 3… senza buchi), date in B (facoltative), tipo in C, prescrizioni.</t>
@@ -145,10 +155,19 @@
     <t>Panca (A)</t>
   </si>
   <si>
+    <t>Panca var. (C)</t>
+  </si>
+  <si>
     <t>Stacco (B)</t>
   </si>
   <si>
-    <t>Panca var. (C)</t>
+    <t>tipo alzata</t>
+  </si>
+  <si>
+    <t>stressante</t>
+  </si>
+  <si>
+    <t>rigenerante</t>
   </si>
   <si>
     <t>Blocco 1 – ESEMPIO</t>
@@ -626,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -690,6 +709,11 @@
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -709,12 +733,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2">
         <v>180</v>
@@ -722,7 +746,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
         <v>120</v>
@@ -730,7 +754,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2">
         <v>210</v>
@@ -738,7 +762,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <f>SUM(B3:B5)</f>
@@ -753,10 +777,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="7" width="24" customWidth="1"/>
@@ -764,72 +788,94 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="str">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="str">
         <f>"4x5 "&amp;MROUND(Massimali!$B$3*0.75,2.5)&amp;"kg"</f>
         <v>4x5 135kg</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E4" s="2" t="str">
         <f>"5x5 "&amp;MROUND(Massimali!$B$4*0.72,2.5)&amp;"kg"</f>
         <v>5x5 87,5kg</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="str">
+      <c r="F4" s="2" t="str">
         <f>MROUND(Massimali!$B$4*0.65,2.5)&amp;"kg 30-35RT"</f>
         <v>77,5kg 30-35RT</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: normale, scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara" sqref="C2:C400">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: normale, scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara" sqref="C3:C400">
       <formula1>"normale,scarico,transizione,ramping,intensificazione,picco,taper,entrata,test,gara"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: stressante, rigenerante, tecnica, stimolo, volume" sqref="D2:G2">
+      <formula1>"stressante,rigenerante,tecnica,stimolo,volume"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -854,45 +900,45 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G2" s="2">
         <v>3</v>
@@ -900,20 +946,20 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2">
         <v>3</v>
@@ -921,20 +967,20 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G4" s="2">
         <v>3</v>
@@ -963,7 +1009,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B1">
         <v>2</v>
